--- a/AAII_Financials/Quarterly/ES_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ES_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
   <si>
     <t>ES</t>
   </si>
@@ -656,344 +656,351 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2903200</v>
+      </c>
+      <c r="E8" s="3">
         <v>4504400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3370200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3220600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2838100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4118400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2971500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3063200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2533500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3332600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2694200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2791500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2629300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3795600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3029400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3208700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2565800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3413300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2465000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2432800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2122500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2825800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2236700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2341900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1951200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2371700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2046800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2170600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1886700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2418100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2023300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2271000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1865200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2314000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1895500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1988500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1762800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2105100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1776600</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2039700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1420000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2025200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1601300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1567600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1286300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1827800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1315900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1428300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1305900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1698900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1448500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1669300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1588400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2357800</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1069,53 +1076,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1483200</v>
+      </c>
+      <c r="E10" s="3">
         <v>2479200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1768900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1653000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1551800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2290600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1655600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1634900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1227700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1633700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1245800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1122200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1041000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1437800</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1191,8 +1201,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,121 +1496,124 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>114800</v>
+      </c>
+      <c r="E14" s="3">
         <v>-300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>286800</v>
-      </c>
-      <c r="G14" s="3">
-        <v>2000</v>
       </c>
       <c r="H14" s="3">
         <v>2000</v>
       </c>
       <c r="I14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J14" s="3">
         <v>-2400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>466100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1770500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-2700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>402400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-6900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-6800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-58000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-16900</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="3">
         <v>2800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-5200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>241800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>2300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-11700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-400</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>11300</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>26000</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AM14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
+      <c r="AN14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AO14" s="3">
         <v>0</v>
@@ -1601,130 +1621,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>379600</v>
+      </c>
+      <c r="E15" s="3">
         <v>823200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>571100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>503600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>494700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>835000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>588200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>610100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>240500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>337600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>291700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>185500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>101600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>236900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>308500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>302100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>294200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>289300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>280800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>276800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>274600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>270700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>260200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>244500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>240500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>236200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>228600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>222600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>219100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>214900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>207900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>208700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>199100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>204300</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>202700</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>194500</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>189900</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>186800</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>183700</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>181300</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2208700</v>
+      </c>
+      <c r="E17" s="3">
         <v>3384000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2624100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2496300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2139500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3159400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2597600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2419200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1901000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2458800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2099400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2232400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2035400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3011300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2507200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2651500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2110300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2750300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1992200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1949500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1670900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2240300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1782000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1780700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1517600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1832600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1611200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1661400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1735700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1923400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1623200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1805000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1473800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1871400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1451700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1493300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1314600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1604200</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1338600</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1529800</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>694500</v>
+      </c>
+      <c r="E18" s="3">
         <v>1120300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>746100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>724300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>698500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>959000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>373800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>644000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>632500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>873800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>594800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>559100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>594000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>784400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>522200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>557200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>455500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>663000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>472800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>483300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>451600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>585500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>454700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>561200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>433600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>539100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>435600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>509200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>151000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>494700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>400100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>466000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>391400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>442600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>443800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>495200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>448200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>500900</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>438000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>509900</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>121500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-28300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-37000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-23600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-31100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-27700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-31000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-44200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-47100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-34000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-27700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-23800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-41600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-32800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>90900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>89900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>93900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>71600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>36700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>43800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>46700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>34200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>25100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>29300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>30300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>24100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>28900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>27000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>45900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>31000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>27700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>16700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>50100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>33800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>28700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>28500</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>29000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>21700</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>22200</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>13600</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>952700</v>
+      </c>
+      <c r="E21" s="3">
         <v>1971900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1354200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1251500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1224300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1821800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>993100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1298300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>920000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1245400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>914200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>768400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>737100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1054100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>921600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>949300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>843700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1023900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>790300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>803900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>772900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>890500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>740000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>834900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>704400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>799400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>693200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>758800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>415900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>740600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>635600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>691400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>640600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>680600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>675200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>718300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>667100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>709400</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>643900</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>704800</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>355500</v>
+      </c>
+      <c r="E22" s="3">
         <v>365300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>331200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>318100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>293200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>300800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>288700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>300600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>271300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>250700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>231300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>222300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>207300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>194500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>186800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>178200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>160100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>153200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>151200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>148000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>145400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>137800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>135400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>134100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>134300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>134700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>133500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>135200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>132700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>131700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>126100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>125200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>126400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>121100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>102300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>108700</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>107300</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>103400</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>102400</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>99900</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>135400</v>
+      </c>
+      <c r="E23" s="3">
         <v>812000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>484600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>172400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>465200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>717900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>150800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-39600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>446500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>686300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1353700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>387400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>47200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>644000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>426300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>469000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>389300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>581400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>358300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>379100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>352800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>482000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>344400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>456400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>329600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>428500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>331000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>401000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>64100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>394000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>301700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>357500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>315100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>355200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>370300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>415100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>369900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>419200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>357900</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>423600</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>79900</v>
+      </c>
+      <c r="E24" s="3">
         <v>203300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>61400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-197000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>110600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>165200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>76400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>76500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>109200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>162500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-67100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>45900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>29900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>151000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>104300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>117700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>95600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>136000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>49800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>94100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>86400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>114000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>70600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>108200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>75500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>91900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>79100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>80200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>30800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>83400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>63500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>66300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>70500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>83800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>131000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>152800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>137300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>157800</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>126800</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>156400</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>55600</v>
+      </c>
+      <c r="E26" s="3">
         <v>608700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>423200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>369400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>354600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>552700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>74400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-116200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>337200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>523700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1286600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>341500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>17300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>493000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>322000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>351300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>293700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>445300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>308600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>285000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>266400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>368000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>273800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>348100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>254100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>336600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>251900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>320800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>33300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>310600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>238200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>291300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>244600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>271400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>239300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>262300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>232600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>261300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>231100</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>267200</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E27" s="3">
         <v>606800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>421300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>367500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>352700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>550800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>72500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-118100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>335300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>521800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1288500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>339700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>15400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>491200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>320200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>349400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>291900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>443400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>306700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>283200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>264500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>366100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>271900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>346300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>252200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>334800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>250000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>318900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>31500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>308700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>236300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>289400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>242800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>269500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>237400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>260400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>230700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>259500</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>229200</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>265300</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3224,8 +3285,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
@@ -3242,29 +3303,29 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
+        <v>0</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AN29" s="3">
-        <v>0</v>
+      <c r="AN29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AO29" s="3">
         <v>0</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-121500</v>
+      </c>
+      <c r="E32" s="3">
         <v>28300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>37000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>23600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>31100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>27700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>31000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>44200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>47100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>34000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>27700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>23800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>41600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>32800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-90900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-89900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-93900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-71600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-36700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-43800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-46700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-34200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-25100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-29300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-30300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-24100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-28900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-27000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-45900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-31000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-27700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-16700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-50100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-33800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-28700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-28500</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-29000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-21700</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-22200</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-13600</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E33" s="3">
         <v>606800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>421300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>367500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>352700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>550800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>72500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-118100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>335300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>521800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1288500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>339700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>15400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>491200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>320200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>349400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>291900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>443400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>306700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>283200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>264500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>366100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>271900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>346300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>252200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>334800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>250000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>318900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>31500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>308700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>231300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>289400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>242800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>269500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>237400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>260400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>230700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>259500</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>229200</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>265300</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E35" s="3">
         <v>606800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>421300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>367500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>352700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>550800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>72500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-118100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>335300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>521800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1288500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>339700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>15400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>491200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>320200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>349400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>291900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>443400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>306700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>283200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>264500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>366100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>271900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>346300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>252200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>334800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>250000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>318900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>31500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>308700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>231300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>289400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>242800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>269500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>237400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>260400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>230700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>259500</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>229200</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>265300</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1819300</v>
+      </c>
+      <c r="E41" s="3">
         <v>270200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>135400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>259300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>343700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>111400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>26700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>97900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>33400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>259200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>53900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>78800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>42200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>36000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>374600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>485700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>29500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>46200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>66800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>88200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>217400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>34100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>106600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>730000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>64900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>47400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>15400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>22700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>20600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>35100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>108100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>59100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>64200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>303800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>38200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>125800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>24600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>45800</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>30300</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>40100</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4463,751 +4553,772 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1906200</v>
+      </c>
+      <c r="E43" s="3">
         <v>2298400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2122200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1819000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1897000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2065600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1893500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1731700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1670000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1789100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1656900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1602100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1513400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1876800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1517100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1453800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1345900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1468600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1226100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1288800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1224100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1290200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1195900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1113500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>996300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1018900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>989400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>993400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>964300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1140300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>994100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1091600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1123800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1086300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>943800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>920000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>833900</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>879500</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>927800</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>967800</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>467200</v>
+      </c>
+      <c r="E44" s="3">
         <v>489400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>491600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>528100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>549200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>604600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>594600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>564200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>532400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>555200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>507300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>445800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>405800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>423300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>374400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>322200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>262400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>287000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>267500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>217300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>187700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>308100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>265600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>214300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>176100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>286500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>235500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>204000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>174100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>277100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>238000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>192500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>171600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>264200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>223100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>305000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>286300</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>361800</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>328700</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>311100</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1905200</v>
+      </c>
+      <c r="E45" s="3">
         <v>1897200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1975100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1899700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1880200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1847900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2246000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2024900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2071700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1889500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1674200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1507900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1382200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1332000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1957100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1657900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1630200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1671900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1709700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1479300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1639700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1514500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1562000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1162600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1168100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1209800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1174300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1000800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>972700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>848300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>952100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>810200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>918000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1117200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1282100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1052700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1185900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>1224400</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>1190900</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>1095700</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6442300</v>
+      </c>
+      <c r="E46" s="3">
         <v>5344700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5077200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4858800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4904800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4912000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5076100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4832900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4672600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4880900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4248000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4009100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3721600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4136400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4223200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3919700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3268000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3473700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3270100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3073600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3268800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3146900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3130100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3220400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2405400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2562700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2414500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2220900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2131700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2300900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2292200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2153400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2277600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2771400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2487100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2403500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>2330800</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>2511400</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>2477700</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2414700</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>308100</v>
+      </c>
+      <c r="E47" s="3">
         <v>314000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>469300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>310700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>304900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>314600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>479000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>484000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1264500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1060000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>984600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3035100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2512100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2617000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2542600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2430600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2120400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1968600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1896600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1822900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1668300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1587000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1563800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1342000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1311300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1295000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1320800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1266500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1149900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1126900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>417500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>586000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>576400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>580400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>585400</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>570300</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>565500</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>561600</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>544600</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>525800</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>45270600</v>
+      </c>
+      <c r="E48" s="3">
         <v>46470200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>45978400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>43044100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>42303400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>41650100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>41042700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>41911500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>41126200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>40289400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>39552100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>38518300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>37578200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>36744900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>36169700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>35029500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>34407200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>33852600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>33424900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>32467100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>31878600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>31265800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>30937700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>29093000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>28610800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>28041400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>27635400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>26964200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>26359000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>26089500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>25610400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>24967700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>24476900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>23958700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>23617500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>22537300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>22071500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>21641900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>21350500</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>20807900</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>4233800</v>
+        <v>3571300</v>
       </c>
       <c r="E49" s="3">
         <v>4233800</v>
       </c>
       <c r="F49" s="3">
-        <v>3571300</v>
+        <v>4233800</v>
       </c>
       <c r="G49" s="3">
         <v>3571300</v>
@@ -5219,10 +5330,10 @@
         <v>3571300</v>
       </c>
       <c r="J49" s="3">
+        <v>3571300</v>
+      </c>
+      <c r="K49" s="3">
         <v>4526700</v>
-      </c>
-      <c r="K49" s="3">
-        <v>4532100</v>
       </c>
       <c r="L49" s="3">
         <v>4532100</v>
@@ -5231,10 +5342,10 @@
         <v>4532100</v>
       </c>
       <c r="N49" s="3">
+        <v>4532100</v>
+      </c>
+      <c r="O49" s="3">
         <v>4530100</v>
-      </c>
-      <c r="O49" s="3">
-        <v>4522600</v>
       </c>
       <c r="P49" s="3">
         <v>4522600</v>
@@ -5243,34 +5354,34 @@
         <v>4522600</v>
       </c>
       <c r="R49" s="3">
-        <v>4477800</v>
+        <v>4522600</v>
       </c>
       <c r="S49" s="3">
         <v>4477800</v>
       </c>
       <c r="T49" s="3">
+        <v>4477800</v>
+      </c>
+      <c r="U49" s="3">
         <v>4477100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4477300</v>
-      </c>
-      <c r="V49" s="3">
-        <v>4453600</v>
       </c>
       <c r="W49" s="3">
         <v>4453600</v>
       </c>
       <c r="X49" s="3">
+        <v>4453600</v>
+      </c>
+      <c r="Y49" s="3">
         <v>4453100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4446000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4403700</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>4427300</v>
       </c>
       <c r="AB49" s="3">
         <v>4427300</v>
@@ -5303,7 +5414,7 @@
         <v>4427300</v>
       </c>
       <c r="AL49" s="3">
-        <v>3519400</v>
+        <v>4427300</v>
       </c>
       <c r="AM49" s="3">
         <v>3519400</v>
@@ -5317,8 +5428,11 @@
       <c r="AP49" s="3">
         <v>3519400</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>3519400</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2582400</v>
+      </c>
+      <c r="E52" s="3">
         <v>2576700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2309500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5078700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4963200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4848600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4544500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1825100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1761100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1720600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1580500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1852000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1814500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1676300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5772800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5741900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5642800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5517100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5423300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6196900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5965400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6065500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6022000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5448300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5284000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5322700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5326000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>4846600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>4928000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>4996500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5493800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>5381400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>5486200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>5302100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>5103100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>4133200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>4171700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>4120900</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>4160900</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>3814500</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>63415700</v>
+      </c>
+      <c r="E54" s="3">
         <v>64707600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>63786700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>61702600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>60956100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>60194700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>59594500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>58573300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>58352500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>57322200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>55612200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>56293300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>54539700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>54105200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>53230900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>51599400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>49916200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>49289200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>48492100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>48014100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>47234600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>46518200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>46099600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>43507300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>42038700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>41649000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>41123900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>39725400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>38995900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>38941000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>38241300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>37515700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>37244300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>37040000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>36220400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>33163600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>32658800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>32355200</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>32053200</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>31082300</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1605100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1662000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1859700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1483600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1512900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1488700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1736900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1562200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1759300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1663700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1869200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1642200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1550000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1821900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2113900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1459600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1353500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1494400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1672200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1289200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1061100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1060900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1370600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1222100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>952100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>914300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1147900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>892100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>903400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1006800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1120000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1162100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1010400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>984300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1085000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>944000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>587200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>745900</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>884500</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>846400</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2939500</v>
+      </c>
+      <c r="E58" s="3">
         <v>3219300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2996100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2700700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3264100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2883500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3105200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2245200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2773100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3011500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2813400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3644900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2661200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2854200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2809300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2055200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1407500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2529100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2745700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1553100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2845600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3126800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2350700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1181900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1237700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1237100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1262100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1611100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1553800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2328500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1799700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1506800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1608800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2146600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1637700</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>975900</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>2421400</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1749400</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1922400</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>1108400</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3107100</v>
+      </c>
+      <c r="E59" s="3">
         <v>3328400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2572500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2305200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1743200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1845800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1537400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1504400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1393000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1692500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1398300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1832600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1583400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1729000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1876000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1972400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1499600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1577800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1429200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1415800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1197900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1351200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1193600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1230100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1136300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1244200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1195600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1245700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1054900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1224100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1193200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>961400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>910300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>965100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>866300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>700500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>777200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>838500</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>831700</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>687300</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8054800</v>
+      </c>
+      <c r="E60" s="3">
         <v>8209700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7808500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6798300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6881000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6516900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6721000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5619800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6253100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6367600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6341400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7119600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5794600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6405000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6799300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5487200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4260500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5601300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5847000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4258100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5104600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5538900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4915000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3634100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3326100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3395600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3605600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3748900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3512100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4559400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4112900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3630300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3529600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>4096000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3589000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2620400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>3785700</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>3333800</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>3638600</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2642000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>26868200</v>
+      </c>
+      <c r="E61" s="3">
         <v>27120400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>27247900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>27135300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>26515500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>26551200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>26133500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>26295500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>26181800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>25275500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>24067200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>22454500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>22160900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>20951500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>20188700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>20242500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>20015900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>18344600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>17532700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>17874000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>16326700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>15258000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>15680400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>15233200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>14216300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>14417100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>14319100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>13989000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>13610200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>12855200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>12832100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>12734900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>12614200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>12016000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>11775900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>10468200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>8899000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>9267900</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>8829400</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>9235100</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6165800</v>
+      </c>
+      <c r="E62" s="3">
         <v>6695900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6629400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5943200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6119100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6131200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6038500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6002000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5568100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5541300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5446700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5520600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5480000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5484100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10614200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>10435100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>10427000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>10351000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>10357000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11314800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>11335900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>11332300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11285100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>10504500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>10535600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>10470700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>10413700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>9710300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>9763400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9733500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>9653900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>9586200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>9671800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>9588700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>9613600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>8921400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>8933000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>8793800</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>8717900</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>8412200</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>46920000</v>
+      </c>
+      <c r="E66" s="3">
         <v>48021100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>47433900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>45518800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>45134700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>44697900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>44399600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>43373300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>43378200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>42623100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>41282800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>40451800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>38830100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>38200200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>37602200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>36164700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>34703500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>34296900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>33736700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>33446900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>32767200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>32129200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>31880500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>29371800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>28077900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>28283500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>28338400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>27448200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>26885700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>27148000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>26598900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>25951300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>25815600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>25700700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>24978600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>22010000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>21617700</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>21395400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>21185900</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>20289400</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7568,7 +7736,7 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
-        <v>155600</v>
+        <v>0</v>
       </c>
       <c r="R70" s="3">
         <v>155600</v>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>155600</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>155600</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4573300</v>
+      </c>
+      <c r="E72" s="3">
         <v>4815800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4505000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4366100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4279900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4203700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3929100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4118700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4496800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4413600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4142500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5666900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5562900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5783000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5527200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5429100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5301100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5229100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5005400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>4906200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>4830100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>4772400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>4613200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>4535900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4384100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4322800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4177000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4100200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>3954500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4092900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>3954000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>3882700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>3753300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>3670600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>3561100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>3474200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>3364300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>3284100</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>3175200</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>3087000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16340200</v>
+      </c>
+      <c r="E76" s="3">
         <v>16531000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16197300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16028300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15665800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15341300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15039400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15044400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14818700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14543600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14173900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15685900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15554100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15749400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15473200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15279200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15057200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14836700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14599800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14411600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14311900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14233400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14063600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13980000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13805300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13210000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12630000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12121600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>11954600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11637400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11486800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>11408800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>11273200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>11183700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>11086200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>10998000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>10885500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>10804200</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>10711700</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>10637400</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E81" s="3">
         <v>606800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>421300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>367500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>352700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>550800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>72500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-118100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>335300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>521800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1288500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>339700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>15400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>491200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>320200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>349400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>291900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>443400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>306700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>283200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>264500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>366100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>271900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>346300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>252200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>334800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>250000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>318900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>31500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>308700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>231300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>289400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>242800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>269500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>237400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>260400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>230700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>259500</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>229200</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>265300</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>385600</v>
+      </c>
+      <c r="E83" s="3">
         <v>379600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>372900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>366100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>354600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>339900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>343400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>329500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>320000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>313000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>308500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>302100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>294200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>289300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>308500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>302100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>294200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>289300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>280800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>276800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>274600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>270700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>260200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>244500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>240500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>236200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>228600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>222600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>219100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>214900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>207900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>208700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>199100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>204300</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>202700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>194500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>189900</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>186800</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>183700</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>181300</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1090500</v>
+      </c>
+      <c r="E89" s="3">
         <v>1324300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>916100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1099600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1057300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1040600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>642100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>555600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>670700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>291300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>477000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>521900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>578100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>69200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>712400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>847100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>469900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>371900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>442300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>712800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>396000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>411400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>186400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>490800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>585100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>420300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>514700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>570300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>496600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>428000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>376300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>709500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>520400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>177700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>512800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>584200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>462600</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>445300</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>524700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>671900</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1014200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1009300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-983300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1126000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1042000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1007400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1188700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1070900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1071500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1149400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1211200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1086100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1062400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-977100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1089100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-803700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-784500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-764600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-963900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-787900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-734200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-689000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-841400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-701400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-674700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-725500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-782500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-751300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-749600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-628100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-638300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-633400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-644300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-607300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-705800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-495300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-623400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-1047100</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-617700</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-490000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1255400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1149900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1013400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1189600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1104000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-999200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1212200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-392500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1484100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1446900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-911800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1561300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1346100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1051600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1202400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1129100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-940800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-858200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1029100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-920300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-793500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-704500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2119600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-619200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-672900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-717600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-822400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-858200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-718000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-875700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-684900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-558400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-667400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-479700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1572400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-459600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-648800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-529800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-789200</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-494800</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,100 +10455,101 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>290300</v>
+      </c>
+      <c r="E96" s="3">
         <v>290000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>276600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>275600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>270600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>270200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>256300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>254300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>246100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>244800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>230100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>229900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>229600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>229400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-216400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-215700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-214000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-213900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-201800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-201400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-201200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-201000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-189000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-188800</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-185200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-181600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-167700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-172200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-153600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-169800</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-160000</v>
       </c>
       <c r="AH96" s="3">
         <v>-160000</v>
@@ -10327,7 +10561,7 @@
         <v>-160000</v>
       </c>
       <c r="AK96" s="3">
-        <v>-150500</v>
+        <v>-160000</v>
       </c>
       <c r="AL96" s="3">
         <v>-150500</v>
@@ -10339,13 +10573,16 @@
         <v>-150500</v>
       </c>
       <c r="AO96" s="3">
+        <v>-150500</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-141000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-141200</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,130 +10953,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-789600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-82800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-23200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>18900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>283800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>31900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>494600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-92900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>585700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1349500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>420300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1042300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>783200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>623400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>409500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>727600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>463000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>429900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>589600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>57600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>589800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>203800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1369100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>780500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>131100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>313900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>272900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>272600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>233700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>393300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>383300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-138400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-93800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>578700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>972000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-23500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>156200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>108800</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>254700</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-175800</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10876,8 +11125,8 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10954,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1556300</v>
+      </c>
+      <c r="E102" s="3">
         <v>91500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-120500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-71100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>237200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>73300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-75500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>70200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-227800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>194000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-14500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>15200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-359000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-80500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>445600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-7900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-56400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-149900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>192400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-89300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-564100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>652100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>43200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>16600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-34800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-15300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>58800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-101000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>74700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>12800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-240800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>276700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-87600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>101100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-25100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>19500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-9800</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>1300</v>
       </c>
     </row>
